--- a/02_加值成品/八上/八上2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-2 純物質與混合物　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上2-2 純物質與混合物　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>有固定組成與性質的物質稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>純物質</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>無法再分解的純物質是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>元素</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>如氧鐵</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>由元素固定比例組成的純物質？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>化合物</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>元素</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>如水</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>兩種以上純物質混合成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>空氣是混合物</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>比例不固定</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>空氣屬於哪類？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>多種氣體</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>水(H₂O)屬於哪類？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>化合物</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>固定比例</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>氧氣屬於哪類？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>元素</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>空氣是混合物</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>單一種類</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>海水屬於哪類？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>空氣是混合物</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>含鹽等</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>二氧化碳是純物質還混合物？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>純物質(化合物)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>元素(同素異形體)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>成分比例不固定、無化學鍵定比</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>純物質沸點固定</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>固定比例</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>多種物質混合且比例不定的是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>元素</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-2 純物質與混合物　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上2-2 純物質與混合物　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>化合物能分解成什麼？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>元素</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>可再分</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>元素能再分解嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>最基本</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>混合物各成分性質如何？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>保留原性質</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>空氣是混合物</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>未反應</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>純物質有固定沸點嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>空氣是混合物</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>不鏽鋼(合金)屬於哪類？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>元素</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>金屬混合</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>二氧化碳屬於哪類？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>化合物</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>C與O組成</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>糖水屬於哪類？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>糖溶於水</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>金(Au)屬於哪類？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>元素</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>單一元素</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>鐵是元素、化合物還混合物？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>元素</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>單一元素</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>汽水是純物質還混合物？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>多成分</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-2 純物質與混合物　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上2-2 純物質與混合物　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何用沸點判別純物質？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>化合物固定比例、混合物不固定</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>純物質沸點固定</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>成分比例不固定、無化學鍵定比</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>測沸點或導電性</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>混合物不固定</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>化合物與混合物最大差別？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>元素(同素異形體)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>成分比例不固定、無化學鍵定比</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>純物質沸點固定</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>化合物固定比例、混合物不固定</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>組成</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>水電解產生氫和氧說明水是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>元素</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>化合物</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>可分解</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>空氣可液化分離出氮氧說明？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>空氣是混合物</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>物理分離</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>鹽水加熱蒸乾留下鹽，鹽水是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>可分離</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>鑽石與石墨都是碳，屬於？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>化合物固定比例、混合物不固定</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>成分比例不固定、無化學鍵定比</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>元素(同素異形體)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>純物質(化合物)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>同一元素</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何合金不是化合物？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>測沸點或導電性</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>純物質(化合物)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>成分比例不固定、無化學鍵定比</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>化合物固定比例、混合物不固定</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>判別純物質最可靠依據？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>固定的熔沸點與性質</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>純物質(化合物)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>成分比例不固定、無化學鍵定比</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>化合物固定比例、混合物不固定</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>特性值</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>如何判斷透明液體是純水還鹽水？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>純物質沸點固定</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>測沸點或導電性</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>固定的熔沸點與性質</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>元素(同素異形體)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>檢驗</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>空氣能分離出氧氮說明其為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>純物質</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>混合物</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>物理分離</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>固定</t>
+          <t>固定：純物質的組成成分和性質都是固定不變的，這是純物質的定義</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>如氧鐵</t>
+          <t>如氧鐵：元素是無法再用一般化學方法分解成更簡單物質的純物質，例如氧、鐵</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>如水</t>
+          <t>如水：化合物是由兩種以上元素以固定比例結合而成的純物質，例如水就是氫和氧以固定比例組成的化合物</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>比例不固定</t>
+          <t>比例不固定：兩種以上純物質混合在一起、比例可以任意調整的物質稱為混合物</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>多種氣體</t>
+          <t>多種氣體：空氣是由氮氣、氧氣、二氧化碳等多種氣體混合而成，比例不固定，屬於混合物</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>固定比例</t>
+          <t>固定比例：水是由氫和氧原子以固定比例(2:1)結合而成的純物質，屬於化合物</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>單一種類</t>
+          <t>單一種類：氧氣只由一種原子(氧原子)組成，無法再分解成更簡單的物質，屬於元素</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>含鹽等</t>
+          <t>含鹽等：海水中含有水、鹽分及各種礦物質，成分比例因地而異，屬於混合物</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>固定比例</t>
+          <t>固定比例：二氧化碳的化學成分固定，是由碳和氧以固定比例結合而成的化合物，屬於純物質</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>混合：由兩種以上物質混合而成，各成分比例可以任意調整的，稱為混合物</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>可再分</t>
+          <t>可再分：化合物是由多種元素組成的，透過化學方法(如電解)可以把化合物分解回組成它的元素</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>最基本</t>
+          <t>最基本：元素是物質組成中最基本的單位，無法用一般化學方法再分解成更簡單的物質</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>未反應</t>
+          <t>未反應：混合物中各成分只是物理混合在一起，並沒有發生化學反應，所以各自仍保留原本的性質</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>特性：純物質因為組成固定，具有固定的熔點和沸點，這是純物質的重要特性之一</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>金屬混合</t>
+          <t>金屬混合：不鏽鋼是由鐵、鉻、鎳等多種金屬混合而成，比例可調整，屬於混合物</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>C與O組成</t>
+          <t>C與O組成：二氧化碳是由碳和氧兩種元素以固定比例(1:2)結合而成的純物質，屬於化合物</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>糖溶於水</t>
+          <t>糖溶於水：糖水是糖溶解在水中形成的，糖和水的比例可以任意調配，屬於混合物</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>單一元素</t>
+          <t>單一元素：金只由一種原子(金原子)組成，無法再分解，屬於元素</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>單一元素</t>
+          <t>單一元素：鐵只由一種原子(鐵原子)組成，屬於元素，不是由多種元素化合而成的化合物</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>多成分</t>
+          <t>多成分：汽水裡含有水、糖、二氧化碳、香料等多種成分，屬於混合物</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>混合物不固定</t>
+          <t>混合物不固定：純物質因為組成固定，沸騰時溫度會固定不變；混合物因為成分比例不固定，沸騰過程中溫度通常會持續變化，可以用這個差異來判別</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>組成</t>
+          <t>組成：化合物中各元素以固定比例結合，且經過化學反應形成新物質；混合物則是各成分物理混合、比例可任意調整，且未發生化學反應，這是兩者最大的差別</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>可分解</t>
+          <t>可分解：水通電後能分解成氫氣和氧氣兩種元素，證明水是由這兩種元素以固定比例結合而成的化合物</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>物理分離</t>
+          <t>物理分離：空氣可以只靠降溫液化、再利用沸點不同進行物理方法分離出氮氣和氧氣，代表這些成分只是混合在一起，並未產生化學鍵結，所以空氣是混合物</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>可分離</t>
+          <t>可分離：鹽水中的鹽和水只是物理混合，透過加熱蒸發這種物理方法就能把兩者分開，代表鹽水是混合物</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>同一元素</t>
+          <t>同一元素：鑽石和石墨都只由碳原子組成，雖然外觀性質差異很大，但本質上都是碳元素，只是原子排列方式不同(稱為同素異形體)</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>混合：合金中的金屬成分是物理方式混合在一起，彼此之間沒有形成固定比例的化學鍵結，比例可以依需求調整，所以合金屬於混合物而非化合物</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>特性值</t>
+          <t>特性值：純物質因為組成固定，具有固定不變的熔點、沸點等特性值，這是判別是否為純物質最可靠的依據</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>檢驗</t>
+          <t>檢驗：純水的沸點固定在100℃(1大氣壓下)且幾乎不導電；鹽水因為含有溶質，沸點會略高於100℃且能導電，可以用這兩種方法檢驗區分</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>物理分離</t>
+          <t>物理分離：空氣可以用物理方法(如降溫液化再分餾)分離出氧氣、氮氣等成分，代表這些成分只是混合在一起，並未產生化學鍵結，所以空氣是混合物</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-2_三種難度測驗卷.xlsx
@@ -683,17 +683,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>空氣是混合物</t>
+          <t>化合物</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>化合物</t>
+          <t>元素</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>純物質</t>
+          <t>有</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>保留原性質</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>化合物</t>
+          <t>元素</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>元素</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
           <t>化合物</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>空氣是混合物</t>
-        </is>
-      </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>保留原性質</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>元素</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>元素</t>
+          <t>化合物</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>化合物</t>
+          <t>保留原性質</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>混合物</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>純物質</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>混合物</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>元素</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>化合物</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>保留原性質</t>
+          <t>有</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>純物質</t>
+          <t>化合物</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>純物質</t>
+          <t>化合物</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>化合物</t>
+          <t>元素</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1635,22 +1635,22 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>元素</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>空氣是混合物</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>有</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>空氣是混合物</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>純物質</t>
-        </is>
-      </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>保留原性質</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1675,17 +1675,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>化合物</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>保留原性質</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>純物質</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>純物質</t>
+          <t>元素</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
+          <t>保留原性質</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
           <t>不能</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>化合物</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
